--- a/results/0916-all/燕山太行山山麓平原农业区/tech_selected_summary.xlsx
+++ b/results/0916-all/燕山太行山山麓平原农业区/tech_selected_summary.xlsx
@@ -439,181 +439,181 @@
     <t>遵化市</t>
   </si>
   <si>
-    <t>县名</t>
-  </si>
-  <si>
-    <t>技术1</t>
-  </si>
-  <si>
-    <t>技术2</t>
-  </si>
-  <si>
-    <t>技术3</t>
-  </si>
-  <si>
-    <t>技术4</t>
-  </si>
-  <si>
-    <t>技术5</t>
-  </si>
-  <si>
-    <t>技术6</t>
-  </si>
-  <si>
-    <t>技术7</t>
-  </si>
-  <si>
-    <t>技术8</t>
-  </si>
-  <si>
-    <t>技术9</t>
-  </si>
-  <si>
-    <t>技术10</t>
-  </si>
-  <si>
-    <t>技术11</t>
-  </si>
-  <si>
-    <t>技术12</t>
-  </si>
-  <si>
-    <t>技术13</t>
-  </si>
-  <si>
-    <t>技术14</t>
-  </si>
-  <si>
-    <t>技术15</t>
-  </si>
-  <si>
-    <t>技术16</t>
-  </si>
-  <si>
-    <t>技术17</t>
-  </si>
-  <si>
-    <t>技术18</t>
-  </si>
-  <si>
-    <t>技术19</t>
-  </si>
-  <si>
-    <t>技术20</t>
-  </si>
-  <si>
-    <t>技术21</t>
-  </si>
-  <si>
-    <t>技术22</t>
-  </si>
-  <si>
-    <t>技术23</t>
-  </si>
-  <si>
-    <t>技术24</t>
-  </si>
-  <si>
-    <t>技术25</t>
-  </si>
-  <si>
-    <t>技术26</t>
-  </si>
-  <si>
-    <t>技术27</t>
-  </si>
-  <si>
-    <t>技术28</t>
-  </si>
-  <si>
-    <t>技术29</t>
-  </si>
-  <si>
-    <t>技术30</t>
-  </si>
-  <si>
-    <t>技术31</t>
-  </si>
-  <si>
-    <t>技术32</t>
-  </si>
-  <si>
-    <t>技术33</t>
-  </si>
-  <si>
-    <t>技术34</t>
-  </si>
-  <si>
-    <t>技术35</t>
-  </si>
-  <si>
-    <t>技术36</t>
-  </si>
-  <si>
-    <t>技术37</t>
-  </si>
-  <si>
-    <t>技术38</t>
-  </si>
-  <si>
-    <t>技术39</t>
-  </si>
-  <si>
-    <t>技术40</t>
-  </si>
-  <si>
-    <t>技术41</t>
-  </si>
-  <si>
-    <t>技术42</t>
-  </si>
-  <si>
-    <t>技术43</t>
-  </si>
-  <si>
-    <t>技术44</t>
-  </si>
-  <si>
-    <t>技术45</t>
-  </si>
-  <si>
-    <t>技术46</t>
-  </si>
-  <si>
-    <t>技术47</t>
-  </si>
-  <si>
-    <t>技术48</t>
-  </si>
-  <si>
-    <t>技术49</t>
-  </si>
-  <si>
-    <t>技术50</t>
-  </si>
-  <si>
-    <t>技术51</t>
-  </si>
-  <si>
-    <t>技术52</t>
-  </si>
-  <si>
-    <t>技术53</t>
-  </si>
-  <si>
-    <t>技术54</t>
-  </si>
-  <si>
-    <t>技术55</t>
-  </si>
-  <si>
-    <t>技术56</t>
-  </si>
-  <si>
-    <t>技术57</t>
-  </si>
-  <si>
-    <t>总经济成本</t>
+    <t>Counties</t>
+  </si>
+  <si>
+    <t>Tech1</t>
+  </si>
+  <si>
+    <t>Tech2</t>
+  </si>
+  <si>
+    <t>Tech3</t>
+  </si>
+  <si>
+    <t>Tech4</t>
+  </si>
+  <si>
+    <t>Tech5</t>
+  </si>
+  <si>
+    <t>Tech6</t>
+  </si>
+  <si>
+    <t>Tech7</t>
+  </si>
+  <si>
+    <t>Tech8</t>
+  </si>
+  <si>
+    <t>Tech9</t>
+  </si>
+  <si>
+    <t>Tech10</t>
+  </si>
+  <si>
+    <t>Tech11</t>
+  </si>
+  <si>
+    <t>Tech12</t>
+  </si>
+  <si>
+    <t>Tech13</t>
+  </si>
+  <si>
+    <t>Tech14</t>
+  </si>
+  <si>
+    <t>Tech15</t>
+  </si>
+  <si>
+    <t>Tech16</t>
+  </si>
+  <si>
+    <t>Tech17</t>
+  </si>
+  <si>
+    <t>Tech18</t>
+  </si>
+  <si>
+    <t>Tech19</t>
+  </si>
+  <si>
+    <t>Tech20</t>
+  </si>
+  <si>
+    <t>Tech21</t>
+  </si>
+  <si>
+    <t>Tech22</t>
+  </si>
+  <si>
+    <t>Tech23</t>
+  </si>
+  <si>
+    <t>Tech24</t>
+  </si>
+  <si>
+    <t>Tech25</t>
+  </si>
+  <si>
+    <t>Tech26</t>
+  </si>
+  <si>
+    <t>Tech27</t>
+  </si>
+  <si>
+    <t>Tech28</t>
+  </si>
+  <si>
+    <t>Tech29</t>
+  </si>
+  <si>
+    <t>Tech30</t>
+  </si>
+  <si>
+    <t>Tech31</t>
+  </si>
+  <si>
+    <t>Tech32</t>
+  </si>
+  <si>
+    <t>Tech33</t>
+  </si>
+  <si>
+    <t>Tech34</t>
+  </si>
+  <si>
+    <t>Tech35</t>
+  </si>
+  <si>
+    <t>Tech36</t>
+  </si>
+  <si>
+    <t>Tech37</t>
+  </si>
+  <si>
+    <t>Tech38</t>
+  </si>
+  <si>
+    <t>Tech39</t>
+  </si>
+  <si>
+    <t>Tech40</t>
+  </si>
+  <si>
+    <t>Tech41</t>
+  </si>
+  <si>
+    <t>Tech42</t>
+  </si>
+  <si>
+    <t>Tech43</t>
+  </si>
+  <si>
+    <t>Tech44</t>
+  </si>
+  <si>
+    <t>Tech45</t>
+  </si>
+  <si>
+    <t>Tech46</t>
+  </si>
+  <si>
+    <t>Tech47</t>
+  </si>
+  <si>
+    <t>Tech48</t>
+  </si>
+  <si>
+    <t>Tech49</t>
+  </si>
+  <si>
+    <t>Tech50</t>
+  </si>
+  <si>
+    <t>Tech51</t>
+  </si>
+  <si>
+    <t>Tech52</t>
+  </si>
+  <si>
+    <t>Tech53</t>
+  </si>
+  <si>
+    <t>Tech54</t>
+  </si>
+  <si>
+    <t>Tech55</t>
+  </si>
+  <si>
+    <t>Tech56</t>
+  </si>
+  <si>
+    <t>Tech57</t>
+  </si>
+  <si>
+    <t>Total economic cost</t>
   </si>
   <si>
     <t>Feed processing_dairy</t>
@@ -712,10 +712,10 @@
     <t>irrigation (drip irrigation)_vegetable</t>
   </si>
   <si>
-    <t>总经济成本: 78972998.67</t>
-  </si>
-  <si>
-    <t>总经济成本: 0.00</t>
+    <t>78972998.67</t>
+  </si>
+  <si>
+    <t>0.00</t>
   </si>
   <si>
     <t>Biochar_sheep &amp; goat</t>
@@ -742,10 +742,10 @@
     <t>4R(Right rate)_vegetable</t>
   </si>
   <si>
-    <t>总经济成本: 101975021.58</t>
-  </si>
-  <si>
-    <t>总经济成本: 100162.01</t>
+    <t>101975021.58</t>
+  </si>
+  <si>
+    <t>100162.01</t>
   </si>
   <si>
     <t>Increasing feeding level_sheep &amp; goat</t>
@@ -769,7 +769,7 @@
     <t>cover crop (mix)_vegetable</t>
   </si>
   <si>
-    <t>总经济成本: 93820170.82</t>
+    <t>93820170.82</t>
   </si>
   <si>
     <t>chemical amendments_sheep&amp;goat</t>
@@ -781,7 +781,7 @@
     <t>4R(Right type)_maize</t>
   </si>
   <si>
-    <t>总经济成本: 72882230.50</t>
+    <t>72882230.50</t>
   </si>
   <si>
     <t>artificial film cover_pig</t>
@@ -805,7 +805,7 @@
     <t>irrigation (AWD irrigation)_rice</t>
   </si>
   <si>
-    <t>总经济成本: 100333331.75</t>
+    <t>100333331.75</t>
   </si>
   <si>
     <t>Nitrocompounds_dairy</t>
@@ -820,7 +820,7 @@
     <t>irrigation (drip irrigation)_friut</t>
   </si>
   <si>
-    <t>总经济成本: 277445961.07</t>
+    <t>277445961.07</t>
   </si>
   <si>
     <t>chemical amendments_dairy</t>
@@ -844,10 +844,10 @@
     <t>4R(Right type)_wheat</t>
   </si>
   <si>
-    <t>总经济成本: 291601567.60</t>
-  </si>
-  <si>
-    <t>总经济成本: 95076811.72</t>
+    <t>291601567.60</t>
+  </si>
+  <si>
+    <t>95076811.72</t>
   </si>
   <si>
     <t>Organic acid_sheep &amp; goat</t>
@@ -862,7 +862,7 @@
     <t>4R(Right time)_wheat</t>
   </si>
   <si>
-    <t>总经济成本: 108565325.87</t>
+    <t>108565325.87</t>
   </si>
   <si>
     <t>Oil_dairy</t>
@@ -871,22 +871,22 @@
     <t>nitrification inhibitor_pig</t>
   </si>
   <si>
-    <t>总经济成本: 28576773.74</t>
+    <t>28576773.74</t>
   </si>
   <si>
     <t>nitrification inhibitor_sheep&amp;goat</t>
   </si>
   <si>
-    <t>总经济成本: 133938450.41</t>
-  </si>
-  <si>
-    <t>总经济成本: 276487837.77</t>
-  </si>
-  <si>
-    <t>总经济成本: 561150716.44</t>
-  </si>
-  <si>
-    <t>总经济成本: 84232061.84</t>
+    <t>133938450.41</t>
+  </si>
+  <si>
+    <t>276487837.77</t>
+  </si>
+  <si>
+    <t>561150716.44</t>
+  </si>
+  <si>
+    <t>84232061.84</t>
   </si>
   <si>
     <t>Probiotics_pig</t>
@@ -895,16 +895,16 @@
     <t>chemical amendments_pig</t>
   </si>
   <si>
-    <t>总经济成本: 266379730.40</t>
+    <t>266379730.40</t>
   </si>
   <si>
     <t>Frequent removal_sheep&amp;goat</t>
   </si>
   <si>
-    <t>总经济成本: 237926937.32</t>
-  </si>
-  <si>
-    <t>总经济成本: 333500398.59</t>
+    <t>237926937.32</t>
+  </si>
+  <si>
+    <t>333500398.59</t>
   </si>
   <si>
     <t>Probiotics_poultry</t>
@@ -943,85 +943,85 @@
     <t>irrigation (water-saving irrigation)_vegetable</t>
   </si>
   <si>
-    <t>总经济成本: 123917869.43</t>
-  </si>
-  <si>
-    <t>总经济成本: 137267480.97</t>
+    <t>123917869.43</t>
+  </si>
+  <si>
+    <t>137267480.97</t>
   </si>
   <si>
     <t>residue rerention_maize</t>
   </si>
   <si>
-    <t>总经济成本: 129199096.75</t>
-  </si>
-  <si>
-    <t>总经济成本: 66903564.33</t>
+    <t>129199096.75</t>
+  </si>
+  <si>
+    <t>66903564.33</t>
   </si>
   <si>
     <t>Bioflilter_sheep&amp;goat</t>
   </si>
   <si>
-    <t>总经济成本: 785386879.62</t>
-  </si>
-  <si>
-    <t>总经济成本: 470071741.08</t>
+    <t>785386879.62</t>
+  </si>
+  <si>
+    <t>470071741.08</t>
   </si>
   <si>
     <t>Feedstock adjustment_beef cattle</t>
   </si>
   <si>
-    <t>总经济成本: 113423921.37</t>
-  </si>
-  <si>
-    <t>总经济成本: 253522248.11</t>
-  </si>
-  <si>
-    <t>总经济成本: 390487.03</t>
+    <t>113423921.37</t>
+  </si>
+  <si>
+    <t>253522248.11</t>
+  </si>
+  <si>
+    <t>390487.03</t>
   </si>
   <si>
     <t>Urease Inhibitor_dairy</t>
   </si>
   <si>
-    <t>总经济成本: 373847585.86</t>
+    <t>373847585.86</t>
   </si>
   <si>
     <t>Frequent removal_dairy</t>
   </si>
   <si>
-    <t>总经济成本: 625018469.11</t>
+    <t>625018469.11</t>
   </si>
   <si>
     <t>Physical additives_pig</t>
   </si>
   <si>
-    <t>总经济成本: 68376615.37</t>
-  </si>
-  <si>
-    <t>总经济成本: 111473083.35</t>
-  </si>
-  <si>
-    <t>总经济成本: 231865139.09</t>
-  </si>
-  <si>
-    <t>总经济成本: 90905789.12</t>
+    <t>68376615.37</t>
+  </si>
+  <si>
+    <t>111473083.35</t>
+  </si>
+  <si>
+    <t>231865139.09</t>
+  </si>
+  <si>
+    <t>90905789.12</t>
   </si>
   <si>
     <t>EEF(DI)_wheat</t>
   </si>
   <si>
-    <t>总经济成本: 306941749.33</t>
+    <t>306941749.33</t>
   </si>
   <si>
     <t>Yucca extract_Beef cattle</t>
   </si>
   <si>
-    <t>总经济成本: 109722586.25</t>
-  </si>
-  <si>
-    <t>总经济成本: 106461608.63</t>
-  </si>
-  <si>
-    <t>总经济成本: 218576278.07</t>
+    <t>109722586.25</t>
+  </si>
+  <si>
+    <t>106461608.63</t>
+  </si>
+  <si>
+    <t>218576278.07</t>
   </si>
   <si>
     <t>manure（high）≥70%_rice</t>
@@ -1036,13 +1036,13 @@
     <t>irrigation (water-saving irrigation)_wheat</t>
   </si>
   <si>
-    <t>总经济成本: 312687079.54</t>
-  </si>
-  <si>
-    <t>总经济成本: 124195802.59</t>
-  </si>
-  <si>
-    <t>总经济成本: 359602220.56</t>
+    <t>312687079.54</t>
+  </si>
+  <si>
+    <t>124195802.59</t>
+  </si>
+  <si>
+    <t>359602220.56</t>
   </si>
   <si>
     <t>tillage management (zero tillage)_rice</t>
@@ -1051,100 +1051,100 @@
     <t>irrigation (water-saving irrigation)_rice</t>
   </si>
   <si>
-    <t>总经济成本: 258047289.81</t>
+    <t>258047289.81</t>
   </si>
   <si>
     <t>Frequent removal_beef cattle</t>
   </si>
   <si>
-    <t>总经济成本: 162750507.30</t>
-  </si>
-  <si>
-    <t>总经济成本: 215808407.10</t>
-  </si>
-  <si>
-    <t>总经济成本: 164564885.91</t>
-  </si>
-  <si>
-    <t>总经济成本: 114070394.13</t>
-  </si>
-  <si>
-    <t>总经济成本: 82527022.84</t>
-  </si>
-  <si>
-    <t>总经济成本: 212364834.03</t>
+    <t>162750507.30</t>
+  </si>
+  <si>
+    <t>215808407.10</t>
+  </si>
+  <si>
+    <t>164564885.91</t>
+  </si>
+  <si>
+    <t>114070394.13</t>
+  </si>
+  <si>
+    <t>82527022.84</t>
+  </si>
+  <si>
+    <t>212364834.03</t>
   </si>
   <si>
     <t>cover crop (non-leguminous)_wheat</t>
   </si>
   <si>
-    <t>总经济成本: 229974006.71</t>
-  </si>
-  <si>
-    <t>总经济成本: 164215612.45</t>
-  </si>
-  <si>
-    <t>总经济成本: 257658740.23</t>
+    <t>229974006.71</t>
+  </si>
+  <si>
+    <t>164215612.45</t>
+  </si>
+  <si>
+    <t>257658740.23</t>
   </si>
   <si>
     <t>tillage management (zero tillage)_maize</t>
   </si>
   <si>
-    <t>总经济成本: 103244903.31</t>
-  </si>
-  <si>
-    <t>总经济成本: 183055065.65</t>
-  </si>
-  <si>
-    <t>总经济成本: 270448949.72</t>
-  </si>
-  <si>
-    <t>总经济成本: 90323609.19</t>
-  </si>
-  <si>
-    <t>总经济成本: 73195926.30</t>
+    <t>103244903.31</t>
+  </si>
+  <si>
+    <t>183055065.65</t>
+  </si>
+  <si>
+    <t>270448949.72</t>
+  </si>
+  <si>
+    <t>90323609.19</t>
+  </si>
+  <si>
+    <t>73195926.30</t>
   </si>
   <si>
     <t>Algae_sheep &amp; goat</t>
   </si>
   <si>
-    <t>总经济成本: 76907172.69</t>
+    <t>76907172.69</t>
   </si>
   <si>
     <t>surface applied  plus irrigation _poultry</t>
   </si>
   <si>
-    <t>总经济成本: 457054090.61</t>
-  </si>
-  <si>
-    <t>总经济成本: 20436589.99</t>
-  </si>
-  <si>
-    <t>总经济成本: 76647298.74</t>
-  </si>
-  <si>
-    <t>总经济成本: 97950917.79</t>
-  </si>
-  <si>
-    <t>总经济成本: 177679386.45</t>
-  </si>
-  <si>
-    <t>总经济成本: 275411047.04</t>
-  </si>
-  <si>
-    <t>总经济成本: 177857902.90</t>
+    <t>457054090.61</t>
+  </si>
+  <si>
+    <t>20436589.99</t>
+  </si>
+  <si>
+    <t>76647298.74</t>
+  </si>
+  <si>
+    <t>97950917.79</t>
+  </si>
+  <si>
+    <t>177679386.45</t>
+  </si>
+  <si>
+    <t>275411047.04</t>
+  </si>
+  <si>
+    <t>177857902.90</t>
   </si>
   <si>
     <t>manure（low）≤30%_vegetable</t>
   </si>
   <si>
-    <t>总经济成本: 383150097.13</t>
-  </si>
-  <si>
-    <t>总经济成本: 94382073.31</t>
-  </si>
-  <si>
-    <t>总经济成本: 371000077.92</t>
+    <t>383150097.13</t>
+  </si>
+  <si>
+    <t>94382073.31</t>
+  </si>
+  <si>
+    <t>371000077.92</t>
   </si>
   <si>
     <t>Yucca extract_Poultry</t>
@@ -1153,70 +1153,70 @@
     <t>metal salt_Poultry</t>
   </si>
   <si>
-    <t>总经济成本: 123375376.51</t>
+    <t>123375376.51</t>
   </si>
   <si>
     <t>rolller press_pig</t>
   </si>
   <si>
-    <t>总经济成本: 424399163.65</t>
-  </si>
-  <si>
-    <t>总经济成本: 257903123.03</t>
-  </si>
-  <si>
-    <t>总经济成本: 511369458.71</t>
-  </si>
-  <si>
-    <t>总经济成本: 96881010.89</t>
-  </si>
-  <si>
-    <t>总经济成本: 697257000.78</t>
+    <t>424399163.65</t>
+  </si>
+  <si>
+    <t>257903123.03</t>
+  </si>
+  <si>
+    <t>511369458.71</t>
+  </si>
+  <si>
+    <t>96881010.89</t>
+  </si>
+  <si>
+    <t>697257000.78</t>
   </si>
   <si>
     <t>Urease Inhibitor_sheep&amp;goat</t>
   </si>
   <si>
-    <t>总经济成本: 414432515.91</t>
-  </si>
-  <si>
-    <t>总经济成本: 149807628.54</t>
+    <t>414432515.91</t>
+  </si>
+  <si>
+    <t>149807628.54</t>
   </si>
   <si>
     <t>Screw press_pig</t>
   </si>
   <si>
-    <t>总经济成本: 303611196.00</t>
-  </si>
-  <si>
-    <t>总经济成本: 65236727.37</t>
-  </si>
-  <si>
-    <t>总经济成本: 548093831.91</t>
-  </si>
-  <si>
-    <t>总经济成本: 92139821.57</t>
-  </si>
-  <si>
-    <t>总经济成本: 127623083.15</t>
-  </si>
-  <si>
-    <t>总经济成本: 486374908.54</t>
-  </si>
-  <si>
-    <t>总经济成本: 434336300.89</t>
+    <t>303611196.00</t>
+  </si>
+  <si>
+    <t>65236727.37</t>
+  </si>
+  <si>
+    <t>548093831.91</t>
+  </si>
+  <si>
+    <t>92139821.57</t>
+  </si>
+  <si>
+    <t>127623083.15</t>
+  </si>
+  <si>
+    <t>486374908.54</t>
+  </si>
+  <si>
+    <t>434336300.89</t>
   </si>
   <si>
     <t>surface crust cover_beef cattle</t>
   </si>
   <si>
-    <t>总经济成本: 310581736.03</t>
-  </si>
-  <si>
-    <t>总经济成本: 182322421.38</t>
-  </si>
-  <si>
-    <t>总经济成本: 308258094.15</t>
+    <t>310581736.03</t>
+  </si>
+  <si>
+    <t>182322421.38</t>
+  </si>
+  <si>
+    <t>308258094.15</t>
   </si>
   <si>
     <t>surface applied  plus irrigation _sheep&amp;goat</t>
@@ -1225,13 +1225,13 @@
     <t>Plant-derived N substitution_maize</t>
   </si>
   <si>
-    <t>总经济成本: 650980424.91</t>
-  </si>
-  <si>
-    <t>总经济成本: 139729546.88</t>
-  </si>
-  <si>
-    <t>总经济成本: 255473141.70</t>
+    <t>650980424.91</t>
+  </si>
+  <si>
+    <t>139729546.88</t>
+  </si>
+  <si>
+    <t>255473141.70</t>
   </si>
 </sst>
 </file>
